--- a/InputFiles/C3DC/TC01_C3DC_phs002371_SexAtBirth-Male.xlsx
+++ b/InputFiles/C3DC/TC01_C3DC_phs002371_SexAtBirth-Male.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
 WITH s, num_of_participants, count(DISTINCT sm) AS num_of_samples
 OPTIONAL MATCH (d:diagnosis)-[:of_diagnosis]-&gt;(dp:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s)
 WITH s, num_of_participants, num_of_samples, d.diagnosis AS diagnosis_name, count(DISTINCT dp) AS diagnosis_n
-ORDER BY diagnosis_n DESC, diagnosis_name
+ORDER BY diagnosis_n DESC, diagnosis_name DESC
 WITH s, num_of_participants, num_of_samples,
      [item IN collect(CASE WHEN diagnosis_name IS NULL THEN null ELSE diagnosis_name + ' (' + toString(diagnosis_n) + ')' END) WHERE item IS NOT NULL] AS diagnosis_all
 WITH s, num_of_participants, num_of_samples,
@@ -571,32 +571,18 @@
      size(diagnosis_all) &gt; 5 AS diagnosis_more
 OPTIONAL MATCH (d2:diagnosis)-[:of_diagnosis]-&gt;(dp2:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s)
 UNWIND CASE WHEN d2 IS NULL THEN [null] ELSE coalesce(d2.anatomic_site, [null]) END AS site
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site, count(DISTINCT dp2) AS site_n
-ORDER BY site_n DESC, site
+WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site, count(DISTINCT d2) AS site_n
+ORDER BY site_n DESC, site DESC
 WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more,
      [item IN collect(CASE WHEN site IS NULL THEN null ELSE site + ' (' + toString(site_n) + ')' END) WHERE item IS NOT NULL] AS site_all
 WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more,
      site_all[0..5] AS site_items,
      size(site_all) &gt; 5 AS site_more
-OPTIONAL MATCH (sf)-[:of_sequencing_file|of_clinical_measure_file|of_cytogenomic_file|of_generic_file|of_methylation_array_file|of_pathology_file]-&gt;(:sample)-[:of_sample]-&gt;(:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s)
+OPTIONAL MATCH (s)&lt;-[*..6]-(fl)
+WHERE (fl:clinical_measure_file OR fl:generic_file OR fl:sequencing_file OR fl:pathology_file OR fl:radiology_file OR fl:methylation_array_file OR fl:cytogenomic_file)
 WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
-     sf.file_type AS file_type, count(DISTINCT sf) AS type_n
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
-     [item IN collect(CASE WHEN file_type IS NULL OR type_n = 0 THEN null ELSE {t: file_type, n: type_n} END) WHERE item IS NOT NULL] AS sample_file_types
-OPTIONAL MATCH (pf)-[:of_clinical_measure_file|of_generic_file|of_radiology_file]-&gt;(:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s)
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more, sample_file_types,
-     pf.file_type AS file_type, count(DISTINCT pf) AS type_n
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more, sample_file_types,
-     [item IN collect(CASE WHEN file_type IS NULL OR type_n = 0 THEN null ELSE {t: file_type, n: type_n} END) WHERE item IS NOT NULL] AS participant_file_types
-OPTIONAL MATCH (stf)-[:of_clinical_measure_file|of_generic_file]-&gt;(s)
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more, sample_file_types, participant_file_types,
-     stf.file_type AS file_type, count(DISTINCT stf) AS type_n
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
-     sample_file_types + participant_file_types + [item IN collect(CASE WHEN file_type IS NULL OR type_n = 0 THEN null ELSE {t: file_type, n: type_n} END) WHERE item IS NOT NULL] AS file_types
-UNWIND CASE WHEN size(file_types) = 0 THEN [{t: null, n: 0}] ELSE file_types END AS ft
-WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
-     ft.t AS file_type, sum(ft.n) AS type_n
-ORDER BY type_n DESC, file_type
+     fl.file_type AS file_type, count(DISTINCT fl.dcf_indexd_guid) AS type_n
+ORDER BY type_n DESC
 WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
      sum(CASE WHEN file_type IS NULL THEN 0 ELSE type_n END) AS num_of_files,
      [item IN collect(CASE WHEN file_type IS NULL THEN null ELSE file_type + ' (' + toString(type_n) + ')' END) WHERE item IS NOT NULL] AS file_type_all
@@ -702,7 +688,7 @@
   MATCH (t:treatment_chemotherapy)-[:of_treatment_chemotherapy]-&gt;(p:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s:study)
   WHERE s.dbgap_accession = 'phs002371' AND p.sex_at_birth = 'Male'
   RETURN p.participant_id AS participant_id,
-         t.guid AS treatment_id,
+         t.treatment_chemotherapy_id AS treatment_id,
          CASE WHEN t.age_at_treatment_start IS NULL OR t.age_at_treatment_start = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_start) END AS age_start,
          CASE WHEN t.age_at_treatment_end IS NULL OR t.age_at_treatment_end = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_end) END AS age_end,
          reduce(text = '', item IN coalesce(t.treatment_type, []) | CASE WHEN text = '' THEN item ELSE text + ', ' + item END) AS treatment_type,
@@ -712,7 +698,7 @@
   MATCH (t:treatment_radiation)-[:of_treatment_radiation]-&gt;(p:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s:study)
   WHERE s.dbgap_accession = 'phs002371' AND p.sex_at_birth = 'Male'
   RETURN p.participant_id AS participant_id,
-         t.guid AS treatment_id,
+         t.treatment_radiation_id AS treatment_id,
          CASE WHEN t.age_at_treatment_start IS NULL OR t.age_at_treatment_start = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_start) END AS age_start,
          CASE WHEN t.age_at_treatment_end IS NULL OR t.age_at_treatment_end = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_end) END AS age_end,
          reduce(text = '', item IN coalesce(t.treatment_type, []) | CASE WHEN text = '' THEN item ELSE text + ', ' + item END) AS treatment_type,
@@ -722,7 +708,7 @@
   MATCH (t:treatment_surgery)-[:of_treatment_surgery]-&gt;(p:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s:study)
   WHERE s.dbgap_accession = 'phs002371' AND p.sex_at_birth = 'Male'
   RETURN p.participant_id AS participant_id,
-         t.guid AS treatment_id,
+         t.treatment_surgery_id AS treatment_id,
          CASE WHEN t.age_at_treatment_start IS NULL OR t.age_at_treatment_start = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_start) END AS age_start,
          CASE WHEN t.age_at_treatment_end IS NULL OR t.age_at_treatment_end = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_end) END AS age_end,
          reduce(text = '', item IN coalesce(t.treatment_type, []) | CASE WHEN text = '' THEN item ELSE text + ', ' + item END) AS treatment_type,
@@ -732,7 +718,7 @@
   MATCH (t:treatment_other)-[:of_treatment_other]-&gt;(p:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s:study)
   WHERE s.dbgap_accession = 'phs002371' AND p.sex_at_birth = 'Male'
   RETURN p.participant_id AS participant_id,
-         t.guid AS treatment_id,
+         t.treatment_other_id AS treatment_id,
          CASE WHEN t.age_at_treatment_start IS NULL OR t.age_at_treatment_start = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_start) END AS age_start,
          CASE WHEN t.age_at_treatment_end IS NULL OR t.age_at_treatment_end = -999 THEN 'Not Reported' ELSE toString(t.age_at_treatment_end) END AS age_end,
          reduce(text = '', item IN coalesce(t.treatment_type, []) | CASE WHEN text = '' THEN item ELSE text + ', ' + item END) AS treatment_type,
@@ -826,6 +812,37 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FilesTab</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MATCH (p:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s:study)
+WHERE s.dbgap_accession = 'phs002371'
+  AND p.sex_at_birth = 'Male'
+MATCH (sm:sample)-[:of_sample]-&gt;(p)
+MATCH (f)-[:of_sequencing_file|of_clinical_measure_file|of_cytogenomic_file|of_generic_file|of_methylation_array_file|of_pathology_file|of_radiology_file]-&gt;(sm)
+RETURN f.file_name AS `File Name`,
+       reduce(text = '', item IN coalesce(f.data_category, []) | CASE WHEN text = '' THEN item ELSE text + ', ' + item END) AS `Data Category`,
+       f.file_type AS `File Type`,
+       s.dbgap_accession AS `Study ID`,
+       p.participant_id AS `Participant ID`,
+       sm.sample_id AS `Sample ID`,
+       reduce(text = '', site IN coalesce(sm.anatomic_site, []) | CASE WHEN text = '' THEN site ELSE text + ';' + site END) AS `Anatomic Site`,
+       CASE
+         WHEN sm.participant_age_at_collection IS NULL OR sm.participant_age_at_collection = -999 THEN 'Not Reported'
+         ELSE toString(sm.participant_age_at_collection)
+       END AS `Age at Collection`,
+       sm.sample_tumor_status AS `Sample Tumor Status`,
+       sm.tumor_spatial_extent AS `Tumor Spatial Extent`
+ORDER BY f.file_name
+LIMIT 100;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
